--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/27 16:31:28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-12000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>140000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>140000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17177.91</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-12000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17177.91</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29177.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/27 18:02:57</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/27 16:31:28</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>-12000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>140000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>140000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-12000</t>
+          <t>17177.91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>29177.91</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>9177.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
+          <t>08/27 19:09:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -229,83 +229,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/27 18:02:57</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/27 16:31:28</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>-12000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>140000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>140000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>17177.91</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17177</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>9177.91</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/27 16:30:36</t>
+          <t>08/28 11:20:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17177.91</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,140 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/27 19:09:36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>9177</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/27 18:02:57</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/27 16:31:28</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-12000</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6097.56</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>140000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17177.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>17177</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.91</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/28 11:20:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6097.56</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5709.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/28 16:33:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5709</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/28 11:20:29</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5709.56</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/28 11:20:23</t>
+          <t>08/30 14:24:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/28 16:33:50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5709</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/28 11:20:29</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>110000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13253.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6097.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.56</t>
+          <t>13253.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/30 16:00:09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13253.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13253.01</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 14:24:49</t>
+          <t>09/02 15:56:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>9146.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/30 16:00:09</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>13253</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>75000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>9146.34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13253</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.01</t>
+          <t>9146.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/02 17:30:13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>75000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>75000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9146.34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>9146.34</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8146.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/02 17:32:46</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8146</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/02 17:30:13</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>75000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>75000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>9146.34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9146</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8146.34</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.34</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 15:56:45</t>
+          <t>09/03 10:39:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9146.34</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/02 17:32:46</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8146</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/02 17:30:13</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9146.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>9146</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.34</t>
+          <t>16250</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/03 12:10:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>95000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11515.15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/03 10:39:51</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>16250</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16250</t>
+          <t>225000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27765.15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>16250</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27765.15</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/03 13:33:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27765</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>225000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27765.15</t>
+          <t>225000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27765.15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27765</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>27765.15</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.15</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 12:10:27</t>
+          <t>09/04 17:02:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11515.15</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/03 10:39:51</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>16250</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 13:33:33</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>27765</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8750</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>225000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27765.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>27765</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.15</t>
+          <t>8750</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/04 18:26:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8750</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8750</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8750</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8750</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04 17:02:30</t>
+          <t>09/05 16:45:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/04 18:26:30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8750</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>6250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8750</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>6250</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
+++ b/bills/JXZFSP01/-5232387654/f4a41167560c1da214c0838137b6fbba9a9aef9cccf70102efbdd2e4d1e69b64/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/05 19:09:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6250</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
